--- a/resources/templates/system/roro_invoice_packing.xlsx
+++ b/resources/templates/system/roro_invoice_packing.xlsx
@@ -13,7 +13,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'INVOICE'!$20:$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'INVOICE'!$B$1:$L$61</definedName>
   </definedNames>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -45,14 +45,12 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">SSANCAR LTD.,
-63, Seonghyeon-ro, Ilsandong-gu, Goyang-si, 
+    <t>SSANCAR LTD.,
+163 Sangidaehak-ro, Siheung-si,
 Gyeonggi-do, Republic of Korea
-TEL:82-505-355-9977 
-FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
-    </r>
+TEL:82-505-355-9977  
+FAX:82-505-366-9977 
+EMAIL : ssancar9977@gmail.com</t>
   </si>
   <si>
     <r>
@@ -510,87 +508,87 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve"> SUB TOTAL :</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CFR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OCEAN FREIGHT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">인천구항</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ICT ( 020-77-002 )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> GRAND TOTAL :</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">선광신항</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> SNCT  ( 020-12-014 )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Signed By    </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">한진인천</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HJIT  ( 020-12-019 )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PCTC  ( 016-12-033 )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">평택동방아이포트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PNCT  ( 016-12-002 )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> DIESEL </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GASOLIN</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">LPG</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">GASOLIN</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> DIESEL </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PNCT  ( 016-12-002 )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">평택동방아이포트</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PCTC  ( 016-12-033 )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">HJIT  ( 020-12-019 )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">한진인천</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Signed By    </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> SNCT  ( 020-12-014 )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">선광신항</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> GRAND TOTAL :</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ICT ( 020-77-002 )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">인천구항</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">OCEAN FREIGHT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CFR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> SUB TOTAL :</t>
     </r>
   </si>
 </sst>
@@ -2416,23 +2414,14 @@
       <c r="AG2" s="88"/>
     </row>
     <row r="3" spans="1:33" customHeight="1" ht="15.75" s="88" customFormat="1">
-      <c r="B3" s="96" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">SSANCAR LTD.,
-63, Seonghyeon-ro, Ilsandong-gu, Goyang-si, 
-Gyeonggi-do, Republic of Korea
-TEL:82-505-355-9977 
-FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
-          </r>
-        </is>
+      <c r="B3" s="96" t="s">
+        <v>5</v>
       </c>
       <c r="F3" s="97"/>
       <c r="G3" s="84"/>
-      <c r="J3" s="85">
+      <c r="J3" s="85" t="str">
         <f>TODAY()</f>
-        <v>46166</v>
+        <v>0</v>
       </c>
       <c r="L3" s="97"/>
       <c r="N3" s="65" t="inlineStr">
@@ -3193,18 +3182,18 @@
       <c r="H21" s="119">
         <v>4830</v>
       </c>
-      <c r="I21" s="63">
+      <c r="I21" s="63" t="str">
         <f>H21</f>
-        <v>4830</v>
+        <v>0</v>
       </c>
       <c r="J21" s="120"/>
       <c r="K21" s="121"/>
       <c r="L21" s="122">
         <v>1770</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="14" t="str">
         <f>SUM(I21,L21)</f>
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="N21" s="75"/>
       <c r="P21" s="52" t="inlineStr">
@@ -3261,18 +3250,18 @@
       <c r="H22" s="124">
         <v>9330</v>
       </c>
-      <c r="I22" s="63">
+      <c r="I22" s="63" t="str">
         <f>H22</f>
-        <v>9330</v>
+        <v>0</v>
       </c>
       <c r="J22" s="125"/>
       <c r="K22" s="126"/>
       <c r="L22" s="127">
         <v>1670</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="14" t="str">
         <f>SUM(I22,L22)</f>
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="O22" s="5"/>
       <c r="P22" s="57" t="inlineStr">
@@ -3310,14 +3299,14 @@
       <c r="F23" s="42"/>
       <c r="G23" s="35"/>
       <c r="H23" s="133"/>
-      <c r="I23" s="51">
+      <c r="I23" s="51" t="str">
         <f>H23</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J23" s="134"/>
       <c r="K23" s="135"/>
       <c r="L23" s="136"/>
-      <c r="M23" s="14">
+      <c r="M23" s="14" t="str">
         <f>SUM(I23,L23)</f>
         <v>0</v>
       </c>
@@ -3363,14 +3352,14 @@
       <c r="F24" s="42"/>
       <c r="G24" s="35"/>
       <c r="H24" s="139"/>
-      <c r="I24" s="51">
+      <c r="I24" s="51" t="str">
         <f>H24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J24" s="140"/>
       <c r="K24" s="141"/>
       <c r="L24" s="142"/>
-      <c r="M24" s="14">
+      <c r="M24" s="14" t="str">
         <f>SUM(I24,L24)</f>
         <v>0</v>
       </c>
@@ -3420,14 +3409,14 @@
       <c r="F25" s="42"/>
       <c r="G25" s="35"/>
       <c r="H25" s="144"/>
-      <c r="I25" s="51">
+      <c r="I25" s="51" t="str">
         <f>H25</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J25" s="145"/>
       <c r="K25" s="146"/>
       <c r="L25" s="147"/>
-      <c r="M25" s="14">
+      <c r="M25" s="14" t="str">
         <f>SUM(I25,L25)</f>
         <v>0</v>
       </c>
@@ -3474,14 +3463,14 @@
       <c r="F26" s="42"/>
       <c r="G26" s="36"/>
       <c r="H26" s="149"/>
-      <c r="I26" s="51">
+      <c r="I26" s="51" t="str">
         <f>H26</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J26" s="150"/>
       <c r="K26" s="151"/>
       <c r="L26" s="152"/>
-      <c r="M26" s="14">
+      <c r="M26" s="14" t="str">
         <f>SUM(I26,L26)</f>
         <v>0</v>
       </c>
@@ -3530,14 +3519,14 @@
       <c r="F27" s="42"/>
       <c r="G27" s="37"/>
       <c r="H27" s="155"/>
-      <c r="I27" s="51">
+      <c r="I27" s="51" t="str">
         <f>H27</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J27" s="156"/>
       <c r="K27" s="157"/>
       <c r="L27" s="158"/>
-      <c r="M27" s="14">
+      <c r="M27" s="14" t="str">
         <f>SUM(I27,L27)</f>
         <v>0</v>
       </c>
@@ -3584,14 +3573,14 @@
       <c r="F28" s="42"/>
       <c r="G28" s="38"/>
       <c r="H28" s="160"/>
-      <c r="I28" s="51">
+      <c r="I28" s="51" t="str">
         <f>H28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J28" s="161"/>
       <c r="K28" s="162"/>
       <c r="L28" s="163"/>
-      <c r="M28" s="14">
+      <c r="M28" s="14" t="str">
         <f>SUM(I28,L28)</f>
         <v>0</v>
       </c>
@@ -3638,14 +3627,14 @@
       <c r="F29" s="42"/>
       <c r="G29" s="39"/>
       <c r="H29" s="165"/>
-      <c r="I29" s="51">
+      <c r="I29" s="51" t="str">
         <f>H29</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J29" s="166"/>
       <c r="K29" s="167"/>
       <c r="L29" s="168"/>
-      <c r="M29" s="14">
+      <c r="M29" s="14" t="str">
         <f>SUM(I29,L29)</f>
         <v>0</v>
       </c>
@@ -3692,14 +3681,14 @@
       <c r="F30" s="42"/>
       <c r="G30" s="40"/>
       <c r="H30" s="170"/>
-      <c r="I30" s="51">
+      <c r="I30" s="51" t="str">
         <f>H30</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J30" s="171"/>
       <c r="K30" s="172"/>
       <c r="L30" s="173"/>
-      <c r="M30" s="14">
+      <c r="M30" s="14" t="str">
         <f>SUM(I30,L30)</f>
         <v>0</v>
       </c>
@@ -3746,14 +3735,14 @@
       <c r="F31" s="42"/>
       <c r="G31" s="40"/>
       <c r="H31" s="170"/>
-      <c r="I31" s="51">
+      <c r="I31" s="51" t="str">
         <f>H31</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J31" s="171"/>
       <c r="K31" s="172"/>
       <c r="L31" s="173"/>
-      <c r="M31" s="14">
+      <c r="M31" s="14" t="str">
         <f>SUM(I31,L31)</f>
         <v>0</v>
       </c>
@@ -3776,14 +3765,14 @@
       <c r="F32" s="42"/>
       <c r="G32" s="40"/>
       <c r="H32" s="170"/>
-      <c r="I32" s="51">
+      <c r="I32" s="51" t="str">
         <f>H32</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J32" s="171"/>
       <c r="K32" s="172"/>
       <c r="L32" s="173"/>
-      <c r="M32" s="14">
+      <c r="M32" s="14" t="str">
         <f>SUM(I32,L32)</f>
         <v>0</v>
       </c>
@@ -3806,14 +3795,14 @@
       <c r="F33" s="42"/>
       <c r="G33" s="40"/>
       <c r="H33" s="170"/>
-      <c r="I33" s="51">
+      <c r="I33" s="51" t="str">
         <f>H33</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J33" s="171"/>
       <c r="K33" s="172"/>
       <c r="L33" s="173"/>
-      <c r="M33" s="14">
+      <c r="M33" s="14" t="str">
         <f>SUM(I33,L33)</f>
         <v>0</v>
       </c>
@@ -3836,14 +3825,14 @@
       <c r="F34" s="42"/>
       <c r="G34" s="40"/>
       <c r="H34" s="170"/>
-      <c r="I34" s="51">
+      <c r="I34" s="51" t="str">
         <f>H34</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J34" s="171"/>
       <c r="K34" s="172"/>
       <c r="L34" s="173"/>
-      <c r="M34" s="14">
+      <c r="M34" s="14" t="str">
         <f>SUM(I34,L34)</f>
         <v>0</v>
       </c>
@@ -3866,14 +3855,14 @@
       <c r="F35" s="42"/>
       <c r="G35" s="40"/>
       <c r="H35" s="170"/>
-      <c r="I35" s="51">
+      <c r="I35" s="51" t="str">
         <f>H35</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J35" s="171"/>
       <c r="K35" s="172"/>
       <c r="L35" s="173"/>
-      <c r="M35" s="14">
+      <c r="M35" s="14" t="str">
         <f>SUM(I35,L35)</f>
         <v>0</v>
       </c>
@@ -3896,14 +3885,14 @@
       <c r="F36" s="42"/>
       <c r="G36" s="40"/>
       <c r="H36" s="170"/>
-      <c r="I36" s="51">
+      <c r="I36" s="51" t="str">
         <f>H36</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J36" s="171"/>
       <c r="K36" s="172"/>
       <c r="L36" s="173"/>
-      <c r="M36" s="14">
+      <c r="M36" s="14" t="str">
         <f>SUM(I36,L36)</f>
         <v>0</v>
       </c>
@@ -3926,14 +3915,14 @@
       <c r="F37" s="42"/>
       <c r="G37" s="40"/>
       <c r="H37" s="170"/>
-      <c r="I37" s="51">
+      <c r="I37" s="51" t="str">
         <f>H37</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J37" s="171"/>
       <c r="K37" s="172"/>
       <c r="L37" s="173"/>
-      <c r="M37" s="14">
+      <c r="M37" s="14" t="str">
         <f>SUM(I37,L37)</f>
         <v>0</v>
       </c>
@@ -3956,14 +3945,14 @@
       <c r="F38" s="42"/>
       <c r="G38" s="40"/>
       <c r="H38" s="170"/>
-      <c r="I38" s="51">
+      <c r="I38" s="51" t="str">
         <f>H38</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J38" s="171"/>
       <c r="K38" s="172"/>
       <c r="L38" s="173"/>
-      <c r="M38" s="14">
+      <c r="M38" s="14" t="str">
         <f>SUM(I38,L38)</f>
         <v>0</v>
       </c>
@@ -3986,14 +3975,14 @@
       <c r="F39" s="42"/>
       <c r="G39" s="40"/>
       <c r="H39" s="170"/>
-      <c r="I39" s="51">
+      <c r="I39" s="51" t="str">
         <f>H39</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J39" s="171"/>
       <c r="K39" s="172"/>
       <c r="L39" s="173"/>
-      <c r="M39" s="14">
+      <c r="M39" s="14" t="str">
         <f>SUM(I39,L39)</f>
         <v>0</v>
       </c>
@@ -4016,14 +4005,14 @@
       <c r="F40" s="42"/>
       <c r="G40" s="40"/>
       <c r="H40" s="170"/>
-      <c r="I40" s="51">
+      <c r="I40" s="51" t="str">
         <f>H40</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J40" s="171"/>
       <c r="K40" s="172"/>
       <c r="L40" s="173"/>
-      <c r="M40" s="14">
+      <c r="M40" s="14" t="str">
         <f>SUM(I40,L40)</f>
         <v>0</v>
       </c>
@@ -4046,14 +4035,14 @@
       <c r="F41" s="42"/>
       <c r="G41" s="40"/>
       <c r="H41" s="170"/>
-      <c r="I41" s="51">
+      <c r="I41" s="51" t="str">
         <f>H41</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J41" s="171"/>
       <c r="K41" s="172"/>
       <c r="L41" s="173"/>
-      <c r="M41" s="14">
+      <c r="M41" s="14" t="str">
         <f>SUM(I41,L41)</f>
         <v>0</v>
       </c>
@@ -4076,14 +4065,14 @@
       <c r="F42" s="42"/>
       <c r="G42" s="40"/>
       <c r="H42" s="170"/>
-      <c r="I42" s="51">
+      <c r="I42" s="51" t="str">
         <f>H42</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J42" s="171"/>
       <c r="K42" s="172"/>
       <c r="L42" s="173"/>
-      <c r="M42" s="14">
+      <c r="M42" s="14" t="str">
         <f>SUM(I42,L42)</f>
         <v>0</v>
       </c>
@@ -4106,14 +4095,14 @@
       <c r="F43" s="42"/>
       <c r="G43" s="40"/>
       <c r="H43" s="170"/>
-      <c r="I43" s="51">
+      <c r="I43" s="51" t="str">
         <f>H43</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J43" s="171"/>
       <c r="K43" s="172"/>
       <c r="L43" s="173"/>
-      <c r="M43" s="14">
+      <c r="M43" s="14" t="str">
         <f>SUM(I43,L43)</f>
         <v>0</v>
       </c>
@@ -4136,14 +4125,14 @@
       <c r="F44" s="42"/>
       <c r="G44" s="40"/>
       <c r="H44" s="170"/>
-      <c r="I44" s="51">
+      <c r="I44" s="51" t="str">
         <f>H44</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J44" s="171"/>
       <c r="K44" s="172"/>
       <c r="L44" s="173"/>
-      <c r="M44" s="14">
+      <c r="M44" s="14" t="str">
         <f>SUM(I44,L44)</f>
         <v>0</v>
       </c>
@@ -4166,14 +4155,14 @@
       <c r="F45" s="42"/>
       <c r="G45" s="40"/>
       <c r="H45" s="170"/>
-      <c r="I45" s="51">
+      <c r="I45" s="51" t="str">
         <f>H45</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J45" s="171"/>
       <c r="K45" s="172"/>
       <c r="L45" s="173"/>
-      <c r="M45" s="14">
+      <c r="M45" s="14" t="str">
         <f>SUM(I45,L45)</f>
         <v>0</v>
       </c>
@@ -4196,14 +4185,14 @@
       <c r="F46" s="42"/>
       <c r="G46" s="40"/>
       <c r="H46" s="170"/>
-      <c r="I46" s="51">
+      <c r="I46" s="51" t="str">
         <f>H46</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J46" s="171"/>
       <c r="K46" s="172"/>
       <c r="L46" s="173"/>
-      <c r="M46" s="14">
+      <c r="M46" s="14" t="str">
         <f>SUM(I46,L46)</f>
         <v>0</v>
       </c>
@@ -4226,14 +4215,14 @@
       <c r="F47" s="42"/>
       <c r="G47" s="40"/>
       <c r="H47" s="170"/>
-      <c r="I47" s="51">
+      <c r="I47" s="51" t="str">
         <f>H47</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J47" s="171"/>
       <c r="K47" s="172"/>
       <c r="L47" s="173"/>
-      <c r="M47" s="14">
+      <c r="M47" s="14" t="str">
         <f>SUM(I47,L47)</f>
         <v>0</v>
       </c>
@@ -4256,14 +4245,14 @@
       <c r="F48" s="42"/>
       <c r="G48" s="40"/>
       <c r="H48" s="170"/>
-      <c r="I48" s="51">
+      <c r="I48" s="51" t="str">
         <f>H48</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J48" s="171"/>
       <c r="K48" s="172"/>
       <c r="L48" s="173"/>
-      <c r="M48" s="14">
+      <c r="M48" s="14" t="str">
         <f>SUM(I48,L48)</f>
         <v>0</v>
       </c>
@@ -4286,14 +4275,14 @@
       <c r="F49" s="42"/>
       <c r="G49" s="40"/>
       <c r="H49" s="170"/>
-      <c r="I49" s="51">
+      <c r="I49" s="51" t="str">
         <f>H49</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J49" s="171"/>
       <c r="K49" s="172"/>
       <c r="L49" s="173"/>
-      <c r="M49" s="14">
+      <c r="M49" s="14" t="str">
         <f>SUM(I49,L49)</f>
         <v>0</v>
       </c>
@@ -4316,14 +4305,14 @@
       <c r="F50" s="42"/>
       <c r="G50" s="40"/>
       <c r="H50" s="170"/>
-      <c r="I50" s="51">
+      <c r="I50" s="51" t="str">
         <f>H50</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J50" s="171"/>
       <c r="K50" s="172"/>
       <c r="L50" s="173"/>
-      <c r="M50" s="14">
+      <c r="M50" s="14" t="str">
         <f>SUM(I50,L50)</f>
         <v>0</v>
       </c>
@@ -4355,21 +4344,21 @@
       </c>
       <c r="G51" s="89"/>
       <c r="H51" s="175"/>
-      <c r="I51" s="12">
+      <c r="I51" s="12" t="str">
         <f>SUM(I21:I50)</f>
-        <v>14160</v>
-      </c>
-      <c r="J51" s="6">
+        <v>0</v>
+      </c>
+      <c r="J51" s="6" t="str">
         <f>SUM(J21:J50)</f>
         <v>0</v>
       </c>
-      <c r="K51" s="9">
+      <c r="K51" s="9" t="str">
         <f>SUM(K21:K50)</f>
         <v>0</v>
       </c>
-      <c r="L51" s="24">
+      <c r="L51" s="24" t="str">
         <f>SUM(L21:L50)</f>
-        <v>3440</v>
+        <v>0</v>
       </c>
       <c r="M51" s="4"/>
       <c r="O51" s="5"/>
@@ -4406,9 +4395,9 @@
           </r>
         </is>
       </c>
-      <c r="I52" s="26">
+      <c r="I52" s="26" t="str">
         <f>SUM(L51)</f>
-        <v>3440</v>
+        <v>0</v>
       </c>
       <c r="J52" s="179"/>
       <c r="K52" s="5"/>
@@ -4502,9 +4491,9 @@
       </c>
       <c r="G54" s="184"/>
       <c r="H54" s="8"/>
-      <c r="I54" s="13">
+      <c r="I54" s="13" t="str">
         <f>SUM(I51:I53)</f>
-        <v>17600</v>
+        <v>0</v>
       </c>
       <c r="J54" s="185"/>
       <c r="K54" s="7"/>
